--- a/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,2</t>
+          <t>-0,31; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,48</t>
+          <t>-1,21; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,04</t>
+          <t>-1,52; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,26</t>
+          <t>-1,98; 0,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; -0,11</t>
+          <t>-2,24; -0,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,42</t>
+          <t>-1,33; 3,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,85</t>
+          <t>-0,73; 0,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; -0,07</t>
+          <t>-1,36; -0,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,34</t>
+          <t>-0,96; 1,17</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 137,26</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 198,42</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 791,07</t>
+          <t>-100,0; 732,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 208,78</t>
+          <t>-61,73; 223,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,66</t>
+          <t>-100,0; 59,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-96,38; 483,67</t>
+          <t>-94,22; 345,65</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,85</t>
+          <t>-1,0; 0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,43</t>
+          <t>-1,22; 0,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 4,9</t>
+          <t>0,09; 4,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,43</t>
+          <t>0,17; 3,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,9</t>
+          <t>-1,07; 0,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,28</t>
+          <t>-0,95; 1,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,65</t>
+          <t>-0,08; 1,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,44</t>
+          <t>-0,9; 0,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,3</t>
+          <t>-0,07; 2,31</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 358,78</t>
+          <t>-84,44; 355,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 316,51</t>
+          <t>-100,0; 350,58</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-20,36; 1436,84</t>
+          <t>-29,57; 1823,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1247,64</t>
+          <t>-5,43; 979,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,59; 326,54</t>
+          <t>-82,95; 372,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-81,43; 434,52</t>
+          <t>-74,48; 381,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 351,42</t>
+          <t>-16,35; 378,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 135,69</t>
+          <t>-77,72; 116,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 481,04</t>
+          <t>-12,79; 520,21</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,4</t>
+          <t>-0,98; 1,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,06</t>
+          <t>-1,23; 1,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,89</t>
+          <t>-0,88; 1,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,03</t>
+          <t>-0,38; 1,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,64</t>
+          <t>-1,11; 0,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,36</t>
+          <t>-0,66; 1,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,33</t>
+          <t>-0,29; 1,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,61</t>
+          <t>-0,88; 0,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,28</t>
+          <t>-0,35; 1,33</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-76,97; 532,76</t>
+          <t>-78,9; 416,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-84,42; 456,76</t>
+          <t>-87,23; 517,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 750,29</t>
+          <t>-69,87; 793,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,05; 435,15</t>
+          <t>-34,69; 471,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-86,62; 206,69</t>
+          <t>-78,74; 266,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 301,42</t>
+          <t>-51,42; 354,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 278,92</t>
+          <t>-28,07; 301,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,13; 139,14</t>
+          <t>-68,64; 125,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 243,31</t>
+          <t>-32,7; 270,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 3,06</t>
+          <t>-0,32; 3,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,17</t>
+          <t>-0,57; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,99</t>
+          <t>-1,09; 2,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,28</t>
+          <t>-1,31; 2,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,32</t>
+          <t>-2,62; 0,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,75</t>
+          <t>-1,45; 1,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,98</t>
+          <t>-0,43; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,81</t>
+          <t>-1,28; 0,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 1,32</t>
+          <t>-0,9; 1,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-37,64; 506,17</t>
+          <t>-28,98; 629,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,19; 393,42</t>
+          <t>-45,53; 430,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,66; 296,09</t>
+          <t>-60,07; 377,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-52,52; 216,01</t>
+          <t>-50,78; 199,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,19; 43,08</t>
+          <t>-87,0; 31,48</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 165,27</t>
+          <t>-44,24; 155,09</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 199,47</t>
+          <t>-23,55; 208,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,92; 80,63</t>
+          <t>-58,24; 95,64</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,95; 121,4</t>
+          <t>-39,31; 134,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,53</t>
+          <t>-3,7; 0,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -0,07</t>
+          <t>-4,09; -0,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,06</t>
+          <t>-2,17; 2,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 2,72</t>
+          <t>-1,58; 2,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,37; -0,0</t>
+          <t>-3,29; 0,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 3,22</t>
+          <t>-0,52; 3,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,18</t>
+          <t>-1,92; 1,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; -0,45</t>
+          <t>-3,07; -0,51</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,44</t>
+          <t>-0,47; 2,55</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,55; 36,47</t>
+          <t>-77,33; 37,62</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,38; 14,93</t>
+          <t>-91,16; 26,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,0; 133,45</t>
+          <t>-48,83; 140,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 245,88</t>
+          <t>-51,73; 264,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 63,95</t>
+          <t>-100,0; 44,57</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 313,85</t>
+          <t>-20,66; 319,44</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 77,32</t>
+          <t>-54,83; 62,32</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-86,87; -12,65</t>
+          <t>-86,67; -15,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 130,08</t>
+          <t>-16,21; 135,36</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 0,1</t>
+          <t>-5,47; 0,23</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,49; -1,28</t>
+          <t>-6,13; -1,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,12</t>
+          <t>-4,13; 1,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,22</t>
+          <t>-0,36; 4,16</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,6</t>
+          <t>-1,9; 1,62</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,11; 71,72</t>
+          <t>2,14; 68,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,56</t>
+          <t>-2,17; 1,62</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,35; -0,27</t>
+          <t>-3,14; -0,15</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,38; 54,48</t>
+          <t>0,35; 56,98</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-89,58; 16,48</t>
+          <t>-88,41; 20,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,34</t>
+          <t>-94,93; -14,94</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-67,16; 38,35</t>
+          <t>-64,03; 50,22</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 554,16</t>
+          <t>-28,3; 509,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,94; 224,4</t>
+          <t>-79,23; 285,14</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>111,88; —</t>
+          <t>103,1; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-57,78; 76,2</t>
+          <t>-58,69; 78,81</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -0,82</t>
+          <t>-81,72; 0,01</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>10,7; 2528,66</t>
+          <t>9,56; 3080,87</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 5,12</t>
+          <t>-1,66; 5,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,43</t>
+          <t>-3,92; 1,54</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 3,86</t>
+          <t>-1,95; 4,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,34</t>
+          <t>-4,15; 1,66</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,53</t>
+          <t>-4,25; 1,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 5,5</t>
+          <t>-0,18; 5,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,97</t>
+          <t>-2,63; 1,86</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,88</t>
+          <t>-3,63; 0,75</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 4,22</t>
+          <t>-0,09; 4,14</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 481,86</t>
+          <t>-53,73; 471,88</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 258,27</t>
+          <t>-92,42; 197,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,58; 372,51</t>
+          <t>-51,3; 519,79</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-69,42; 52,91</t>
+          <t>-70,81; 73,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,44; 69,12</t>
+          <t>-71,42; 87,65</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 206,91</t>
+          <t>-6,54; 203,11</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-51,37; 91,13</t>
+          <t>-53,61; 78,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-70,57; 37,41</t>
+          <t>-71,1; 35,57</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 166,37</t>
+          <t>-3,59; 167,72</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,73</t>
+          <t>-0,52; 0,74</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,05</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,35</t>
+          <t>-0,06; 1,4</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,18</t>
+          <t>-0,12; 1,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,07</t>
+          <t>-1,19; -0,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,09; 23,6</t>
+          <t>1,05; 23,53</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,84</t>
+          <t>-0,08; 0,82</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,95; -0,14</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,82</t>
+          <t>0,83; 12,91</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 58,24</t>
+          <t>-28,62; 60,0</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 7,22</t>
+          <t>-58,53; 6,72</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 102,16</t>
+          <t>-4,75; 110,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 84,94</t>
+          <t>-6,61; 88,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-57,67; -3,42</t>
+          <t>-60,19; -1,67</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>58,71; 1450,72</t>
+          <t>59,89; 1696,84</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 57,42</t>
+          <t>-5,28; 58,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -12,03</t>
+          <t>-50,91; -7,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>53,77; 918,72</t>
+          <t>51,28; 850,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,43</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,19</t>
+          <t>0,35</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,2</t>
+          <t>-0,26; 2,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,48</t>
+          <t>-1,22; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,0</t>
+          <t>-1,04; 1,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,27</t>
+          <t>-2,21; 0,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,15</t>
+          <t>-2,47; -0,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,96</t>
+          <t>-1,16; 4,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,9</t>
+          <t>-0,77; 0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,36; -0,04</t>
+          <t>-1,34; 0,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,17</t>
+          <t>-0,64; 2,16</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-91,36%</t>
+          <t>-5,71%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-22,53%</t>
+          <t>42,0%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,26</t>
+          <t>-100,0; 145,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 732,27</t>
+          <t>-100,0; 755,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 223,56</t>
+          <t>-63,8; 207,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,21</t>
+          <t>-100,0; 73,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-94,22; 345,65</t>
+          <t>-67,06; 464,9</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,75</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,82</t>
+          <t>-0,97; 0,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,41</t>
+          <t>-1,26; 0,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,51</t>
+          <t>0,23; 5,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,22</t>
+          <t>0,1; 3,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,94</t>
+          <t>-1,05; 1,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,23</t>
+          <t>-0,72; 1,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,65</t>
+          <t>-0,09; 1,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,42</t>
+          <t>-0,89; 0,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,31</t>
+          <t>0,14; 2,86</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>239,9%</t>
+          <t>279,42%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>113,13%</t>
+          <t>155,9%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,44; 355,89</t>
+          <t>-83,06; 315,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 350,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 1823,61</t>
+          <t>-6,93; 1423,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 979,72</t>
+          <t>-14,58; 1005,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,95; 372,77</t>
+          <t>-84,02; 391,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,48; 381,55</t>
+          <t>-67,46; 535,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,35; 378,49</t>
+          <t>-16,65; 397,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-77,72; 116,51</t>
+          <t>-77,91; 113,46</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 520,21</t>
+          <t>-1,34; 581,61</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,51</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,36</t>
+          <t>-1,0; 1,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,03</t>
+          <t>-1,14; 0,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,95</t>
+          <t>-0,83; 1,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 1,93</t>
+          <t>-0,44; 1,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,78</t>
+          <t>-1,23; 0,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,35</t>
+          <t>-0,37; 1,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,37</t>
+          <t>-0,46; 1,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,59</t>
+          <t>-0,9; 0,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 1,33</t>
+          <t>-0,31; 1,33</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 416,71</t>
+          <t>-81,2; 495,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,23; 517,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,87; 793,67</t>
+          <t>-76,73; 540,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,69; 471,44</t>
+          <t>-42,2; 457,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,74; 266,01</t>
+          <t>-81,73; 205,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,42; 354,27</t>
+          <t>-35,39; 439,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 301,39</t>
+          <t>-38,41; 259,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,64; 125,9</t>
+          <t>-67,14; 133,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,7; 270,26</t>
+          <t>-29,07; 245,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>0,51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,14</t>
+          <t>-0,32; 3,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,34</t>
+          <t>-0,64; 2,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 2,15</t>
+          <t>-0,19; 2,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,18</t>
+          <t>-1,33; 2,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,22</t>
+          <t>-2,61; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,67</t>
+          <t>-0,96; 2,06</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,16</t>
+          <t>-0,36; 2,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,94</t>
+          <t>-1,34; 0,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,48</t>
+          <t>-0,16; 2,0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>114,83%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,98; 629,28</t>
+          <t>-30,85; 625,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-45,53; 430,54</t>
+          <t>-43,09; 394,79</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,07; 377,92</t>
+          <t>-21,12; 566,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 199,5</t>
+          <t>-47,52; 231,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-87,0; 31,48</t>
+          <t>-84,92; 48,84</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,24; 155,09</t>
+          <t>-35,23; 200,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 208,58</t>
+          <t>-20,25; 198,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-58,24; 95,64</t>
+          <t>-58,45; 70,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-39,31; 134,64</t>
+          <t>-11,72; 184,15</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,56</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>1,16</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,64</t>
+          <t>-3,68; 0,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,17</t>
+          <t>-4,61; -0,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 2,82</t>
+          <t>-2,01; 2,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,66</t>
+          <t>-1,53; 2,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,1</t>
+          <t>-3,33; 0,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,3</t>
+          <t>-0,31; 3,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,09</t>
+          <t>-2,1; 1,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,51</t>
+          <t>-3,14; -0,45</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 2,55</t>
+          <t>-0,53; 2,61</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>43,37%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-77,33; 37,62</t>
+          <t>-78,03; 48,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-91,16; 26,72</t>
+          <t>-91,51; 13,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-48,83; 140,66</t>
+          <t>-46,51; 131,54</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 264,33</t>
+          <t>-51,98; 247,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,57</t>
+          <t>-94,74; 49,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-20,66; 319,44</t>
+          <t>-14,32; 362,89</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-54,83; 62,32</t>
+          <t>-57,69; 59,28</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-86,67; -15,44</t>
+          <t>-87,77; -9,55</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 135,36</t>
+          <t>-13,54; 150,54</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,23</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,01</t>
+          <t>3,06</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>21,06</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,23</t>
+          <t>-5,71; 0,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -1,23</t>
+          <t>-6,15; -1,02</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 1,13</t>
+          <t>-4,25; 1,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,16</t>
+          <t>-0,47; 4,23</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,62</t>
+          <t>-1,66; 1,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,14; 68,07</t>
+          <t>0,79; 4,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,62</t>
+          <t>-2,18; 1,51</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,15</t>
+          <t>-3,3; -0,24</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,35; 56,98</t>
+          <t>-0,75; 2,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-29,03%</t>
+          <t>-26,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2159,0%</t>
+          <t>188,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>702,32%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-88,41; 20,52</t>
+          <t>-87,97; 32,05</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-94,93; -14,94</t>
+          <t>-95,22; -19,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 50,22</t>
+          <t>-63,41; 56,93</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-28,3; 509,75</t>
+          <t>-30,1; 530,5</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,23; 285,14</t>
+          <t>-71,68; 282,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>103,1; —</t>
+          <t>9,88; 621,23</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-58,69; 78,81</t>
+          <t>-57,63; 71,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-81,72; 0,01</t>
+          <t>-81,56; -4,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9,56; 3080,87</t>
+          <t>-19,88; 135,91</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,06</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,9</t>
+          <t>3,07</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2,19</t>
+          <t>2,24</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,0</t>
+          <t>-1,69; 5,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 1,54</t>
+          <t>-3,9; 1,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,03</t>
+          <t>-1,85; 3,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,66</t>
+          <t>-4,72; 1,25</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 1,85</t>
+          <t>-4,51; 1,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 5,52</t>
+          <t>0,15; 6,05</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 1,86</t>
+          <t>-2,39; 1,92</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,75</t>
+          <t>-3,39; 0,87</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,14</t>
+          <t>-0,19; 4,36</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 471,88</t>
+          <t>-47,3; 485,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-92,42; 197,97</t>
+          <t>-89,78; 204,83</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-51,3; 519,79</t>
+          <t>-50,26; 405,41</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-70,81; 73,0</t>
+          <t>-73,36; 62,71</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-71,42; 87,65</t>
+          <t>-75,47; 63,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 203,11</t>
+          <t>-1,4; 219,55</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,61; 78,69</t>
+          <t>-49,39; 81,2</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-71,1; 35,57</t>
+          <t>-68,66; 36,48</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 167,72</t>
+          <t>-6,92; 173,89</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,74</t>
+          <t>-0,48; 0,78</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,05</t>
+          <t>-1,12; 0,08</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,4</t>
+          <t>0,3; 1,67</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,22</t>
+          <t>-0,16; 1,16</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,03</t>
+          <t>-1,19; -0,06</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,05; 23,53</t>
+          <t>0,93; 2,23</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,82</t>
+          <t>-0,12; 0,82</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; -0,14</t>
+          <t>-0,98; -0,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,91</t>
+          <t>0,79; 1,77</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>399,6%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>234,06%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 60,0</t>
+          <t>-27,2; 62,78</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 6,72</t>
+          <t>-59,67; 9,78</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 110,05</t>
+          <t>13,82; 125,27</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 88,45</t>
+          <t>-8,45; 84,98</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-60,19; -1,67</t>
+          <t>-59,14; -3,13</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>59,89; 1696,84</t>
+          <t>44,78; 162,34</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 58,05</t>
+          <t>-6,74; 58,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-50,91; -7,29</t>
+          <t>-53,75; -12,07</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>51,28; 850,91</t>
+          <t>40,46; 125,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
